--- a/Mixed/transform.xlsx
+++ b/Mixed/transform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8361990-9384-4BAC-B157-4FA8EA835C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D050FEC3-5A96-44FD-A725-E613207AA304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="975" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>る-＞イ段ます</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ウ段-＞イ段ます</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -532,6 +528,10 @@
   </si>
   <si>
     <t>简体：だ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>る-＞ます</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -970,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>9</v>
@@ -985,7 +985,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
@@ -999,14 +999,14 @@
         <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
@@ -1014,14 +1014,14 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1042,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1058,7 +1058,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1071,7 +1071,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1081,14 +1081,14 @@
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
@@ -1096,14 +1096,14 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
@@ -1111,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1150,10 +1150,10 @@
         <v>0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1202,14 +1202,14 @@
         <v>0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
@@ -1217,14 +1217,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
@@ -1232,14 +1232,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -1247,14 +1247,14 @@
         <v>0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1340,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1366,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1405,14 +1405,14 @@
         <v>0</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -1433,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1446,14 +1446,14 @@
         <v>0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
@@ -1461,14 +1461,14 @@
         <v>0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1489,14 +1489,14 @@
         <v>0</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
@@ -1504,14 +1504,14 @@
         <v>0</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
@@ -1519,14 +1519,14 @@
         <v>0</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
@@ -1534,14 +1534,14 @@
         <v>0</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
@@ -1549,10 +1549,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -1562,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -1588,10 +1588,10 @@
         <v>0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -1614,14 +1614,14 @@
         <v>0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
@@ -1629,14 +1629,14 @@
         <v>0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
@@ -1644,14 +1644,14 @@
         <v>0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
@@ -1659,14 +1659,14 @@
         <v>0</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
